--- a/Roadmap/roadmap_churn_2026-2027.xlsx
+++ b/Roadmap/roadmap_churn_2026-2027.xlsx
@@ -968,7 +968,7 @@
       <c r="A13" s="16" t="n"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Pipeline ingestion Bronze→Silver (dbt · Prefect)</t>
+          <t>Pipeline ingestion Bronze→Silver (dbt · Airflow)</t>
         </is>
       </c>
       <c r="C13" s="19" t="n"/>
@@ -1156,7 +1156,7 @@
       <c r="A21" s="16" t="n"/>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Conteneurisation Podman + docker-compose</t>
+          <t>Conteneurisation Docker + docker-compose</t>
         </is>
       </c>
       <c r="C21" s="19" t="n"/>

--- a/Roadmap/roadmap_churn_2026-2027.xlsx
+++ b/Roadmap/roadmap_churn_2026-2027.xlsx
@@ -992,7 +992,7 @@
       <c r="A14" s="20" t="n"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Nettoyage qualité + bases Postgres / Mongo reliées</t>
+          <t>Nettoyage qualité + avis Trustpilot / SDV dans PostgreSQL (JSONB)</t>
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
